--- a/exports/HINDZINC_full_report.xlsx
+++ b/exports/HINDZINC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.26</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>325.65</v>
+        <v>317.8</v>
       </c>
       <c r="I2" t="n">
         <v>318.03138194525</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.53</v>
+        <v>-3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>4.2</v>
+        <v>4.51</v>
       </c>
       <c r="M2" t="n">
         <v>2.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
         <v>-0.32</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>6.25</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44596.38541666666</v>
+        <v>44596.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>327.7</v>
+        <v>329</v>
       </c>
       <c r="I3" t="n">
         <v>328.9390174310063</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.12</v>
+        <v>-3.52</v>
       </c>
       <c r="L3" t="n">
-        <v>3.49</v>
+        <v>4.12</v>
       </c>
       <c r="M3" t="n">
         <v>0.78</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>4.38</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>321.65</v>
+        <v>312.75</v>
       </c>
       <c r="I4" t="n">
         <v>319.9654037007248</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.23</v>
+        <v>-4.94</v>
       </c>
       <c r="L4" t="n">
-        <v>3.53</v>
+        <v>5.74</v>
       </c>
       <c r="M4" t="n">
         <v>1.53</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>6.9</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>311.6</v>
+        <v>334.5</v>
       </c>
       <c r="I5" t="n">
         <v>321.8312032402611</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.37</v>
+        <v>-6.95</v>
       </c>
       <c r="L5" t="n">
-        <v>7.03</v>
+        <v>7.08</v>
       </c>
       <c r="M5" t="n">
         <v>1.43</v>
       </c>
       <c r="N5" t="n">
-        <v>4.09</v>
+        <v>11.62</v>
       </c>
       <c r="O5" t="n">
         <v>-4.06</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.49</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44627.38541666666</v>
+        <v>44627.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>320.5</v>
+        <v>318.8</v>
       </c>
       <c r="I6" t="n">
         <v>319.6143787092873</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.19</v>
+        <v>-4.69</v>
       </c>
       <c r="L6" t="n">
         <v>6.91</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.78</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>320.7</v>
+        <v>324</v>
       </c>
       <c r="I7" t="n">
         <v>322.0353908381832</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6</v>
+        <v>-1.63</v>
       </c>
       <c r="L7" t="n">
         <v>5.9</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>4.4</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>344.3</v>
+        <v>324.75</v>
       </c>
       <c r="I8" t="n">
         <v>333.8508358342501</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>6.27</v>
+        <v>0.23</v>
       </c>
       <c r="L8" t="n">
         <v>0.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0.16</v>
+        <v>0.52</v>
       </c>
       <c r="N8" t="n">
-        <v>2.33</v>
+        <v>5.98</v>
       </c>
       <c r="O8" t="n">
         <v>1.04</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.26</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44705.55208333334</v>
+        <v>44706.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>294.35</v>
+        <v>306.25</v>
       </c>
       <c r="I9" t="n">
         <v>303.4876808412902</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K9" t="n">
-        <v>9.359999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="L9" t="n">
         <v>5.47</v>
@@ -954,7 +1061,7 @@
         <v>1.85</v>
       </c>
       <c r="N9" t="n">
-        <v>3.89</v>
+        <v>4.47</v>
       </c>
       <c r="O9" t="n">
         <v>-5.98</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>10.46</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>288.9</v>
+        <v>280.1</v>
       </c>
       <c r="I10" t="n">
         <v>288.2283997985045</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.67</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>6.01</v>
+        <v>9.06</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="N10" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
         <v>4.47</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>7.83</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44749.55208333334</v>
+        <v>44750.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>256.7</v>
+        <v>262.7</v>
       </c>
       <c r="I11" t="n">
         <v>260.5834108096142</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>8.35</v>
+        <v>6.21</v>
       </c>
       <c r="L11" t="n">
         <v>3.84</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
         <v>3.51</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>6.12</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44761.55208333334</v>
+        <v>44762.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>299.2</v>
+        <v>280.3</v>
       </c>
       <c r="I12" t="n">
         <v>282.6257562770433</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
-        <v>13.89</v>
+        <v>6.7</v>
       </c>
       <c r="L12" t="n">
         <v>0.61</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07000000000000001</v>
+        <v>6.42</v>
       </c>
       <c r="N12" t="n">
-        <v>1.18</v>
+        <v>6.75</v>
       </c>
       <c r="O12" t="n">
         <v>2.45</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.19</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44789.38541666666</v>
+        <v>44789.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>272.8</v>
+        <v>292.6</v>
       </c>
       <c r="I13" t="n">
         <v>278.3646709720813</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>2.68</v>
+        <v>-4.39</v>
       </c>
       <c r="L13" t="n">
-        <v>2.32</v>
+        <v>7.35</v>
       </c>
       <c r="M13" t="n">
         <v>1.55</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.15</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>282.8</v>
+        <v>276.3</v>
       </c>
       <c r="I14" t="n">
         <v>281.5895015011702</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>31</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.35</v>
+        <v>-5.57</v>
       </c>
       <c r="L14" t="n">
         <v>6.85</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.67</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>272.35</v>
+        <v>282</v>
       </c>
       <c r="I15" t="n">
         <v>277.8265537461916</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>1.43</v>
+        <v>-2.06</v>
       </c>
       <c r="L15" t="n">
         <v>3.04</v>
@@ -1296,7 +1475,7 @@
         <v>3.77</v>
       </c>
       <c r="N15" t="n">
-        <v>2.77</v>
+        <v>4.64</v>
       </c>
       <c r="O15" t="n">
         <v>-2.48</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.67</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44887.55208333334</v>
+        <v>44888.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>319.5</v>
+        <v>300.75</v>
       </c>
       <c r="I16" t="n">
         <v>311.1839104846702</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K16" t="n">
-        <v>13.3</v>
+        <v>6.65</v>
       </c>
       <c r="L16" t="n">
         <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>4.82</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>5.79</v>
       </c>
       <c r="O16" t="n">
         <v>4.64</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.28</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44897.55208333334</v>
+        <v>44900.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>306.35</v>
+        <v>312.3</v>
       </c>
       <c r="I17" t="n">
         <v>311.0664905803047</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.86</v>
+        <v>-3.84</v>
       </c>
       <c r="L17" t="n">
-        <v>3.41</v>
+        <v>4.32</v>
       </c>
       <c r="M17" t="n">
         <v>0.57</v>
       </c>
       <c r="N17" t="n">
-        <v>1.22</v>
+        <v>2.71</v>
       </c>
       <c r="O17" t="n">
         <v>-5.79</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>4.9</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>320.5</v>
+        <v>312.45</v>
       </c>
       <c r="I18" t="n">
         <v>317.7712377493263</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>2.63</v>
+        <v>0.05</v>
       </c>
       <c r="L18" t="n">
         <v>1.99</v>
       </c>
       <c r="M18" t="n">
-        <v>0.48</v>
+        <v>2.57</v>
       </c>
       <c r="N18" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
         <v>2.71</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>5.98</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44928.55208333334</v>
+        <v>44929.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>325.25</v>
+        <v>331.75</v>
       </c>
       <c r="I19" t="n">
         <v>330.2902725714003</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.1</v>
+        <v>-6.18</v>
       </c>
       <c r="L19" t="n">
-        <v>5.55</v>
+        <v>7.54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.78</v>
+        <v>1.29</v>
       </c>
       <c r="N19" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="O19" t="n">
         <v>-2.34</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>4.97</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44945.55208333334</v>
+        <v>44946.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>376.8</v>
+        <v>352.1</v>
       </c>
       <c r="I20" t="n">
         <v>354.2394578746629</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K20" t="n">
-        <v>13.58</v>
+        <v>6.13</v>
       </c>
       <c r="L20" t="n">
         <v>1.07</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05</v>
+        <v>8.44</v>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>6.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.77</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.93</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45002.38541666666</v>
+        <v>45002.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>311.05</v>
+        <v>316.7</v>
       </c>
       <c r="I21" t="n">
         <v>313.6512942651856</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>11.66</v>
+        <v>10.05</v>
       </c>
       <c r="L21" t="n">
         <v>2.24</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>7.9</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45013.55208333334</v>
+        <v>45014.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>329.45</v>
+        <v>300.5</v>
       </c>
       <c r="I22" t="n">
         <v>312.8453256731936</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>4.03</v>
+        <v>-5.12</v>
       </c>
       <c r="L22" t="n">
-        <v>2.34</v>
+        <v>6.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05</v>
+        <v>9.24</v>
       </c>
       <c r="N22" t="n">
-        <v>1.94</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>3.8</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>7.65</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45028.55208333334</v>
+        <v>45029.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>312.65</v>
+        <v>319.35</v>
       </c>
       <c r="I23" t="n">
         <v>314.8582093258177</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.04</v>
+        <v>-6.27</v>
       </c>
       <c r="L23" t="n">
-        <v>4.76</v>
+        <v>7.02</v>
       </c>
       <c r="M23" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="N23" t="n">
         <v>2.38</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.24</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45041.38541666666</v>
+        <v>45041.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>317.15</v>
+        <v>316.3</v>
       </c>
       <c r="I24" t="n">
         <v>316.379253402573</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.96</v>
       </c>
       <c r="L24" t="n">
         <v>2.1</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>3.84</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45093.55208333334</v>
+        <v>45096.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>304.8</v>
+        <v>306.5</v>
       </c>
       <c r="I25" t="n">
         <v>306.1435085828055</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>52</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="L25" t="n">
         <v>0.52</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>3.01</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45121.55208333334</v>
+        <v>45124.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>329</v>
+        <v>323.6</v>
       </c>
       <c r="I26" t="n">
         <v>326.9904881390167</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K26" t="n">
-        <v>7.34</v>
+        <v>5.58</v>
       </c>
       <c r="L26" t="n">
         <v>0.82</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45170.55208333334</v>
+        <v>45173.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>319.25</v>
+        <v>323</v>
       </c>
       <c r="I27" t="n">
         <v>322.1417337156238</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K27" t="n">
-        <v>1.34</v>
+        <v>0.19</v>
       </c>
       <c r="L27" t="n">
         <v>1.36</v>
@@ -1980,7 +2303,7 @@
         <v>1.19</v>
       </c>
       <c r="N27" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
         <v>-1.52</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>3.09</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>316</v>
+        <v>314.3</v>
       </c>
       <c r="I28" t="n">
         <v>314.5901686004036</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.17</v>
+        <v>-2.69</v>
       </c>
       <c r="L28" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="M28" t="n">
         <v>-0</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>3.2</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45208.55208333334</v>
+        <v>45209.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>311.95</v>
+        <v>315.7</v>
       </c>
       <c r="I29" t="n">
         <v>314.2655996949998</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K29" t="n">
-        <v>0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="L29" t="n">
         <v>2.93</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>5.05</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45219.38541666666</v>
+        <v>45219.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>310.6</v>
+        <v>309</v>
       </c>
       <c r="I30" t="n">
         <v>309.5450975759321</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.62</v>
+        <v>-2.12</v>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>4.88</v>
       </c>
       <c r="M30" t="n">
         <v>0.25</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4.71</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45246.55208333334</v>
+        <v>45247.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>304.4</v>
+        <v>307</v>
       </c>
       <c r="I31" t="n">
         <v>305.4669121681586</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>1.49</v>
+        <v>0.65</v>
       </c>
       <c r="L31" t="n">
         <v>1.44</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.94</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45274.55208333334</v>
+        <v>45275.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>319.75</v>
+        <v>315</v>
       </c>
       <c r="I32" t="n">
         <v>315.9972543406903</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
-        <v>4.15</v>
+        <v>2.61</v>
       </c>
       <c r="L32" t="n">
         <v>3.09</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>4.14</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45289.38541666666</v>
+        <v>45289.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>315</v>
+        <v>317.8</v>
       </c>
       <c r="I33" t="n">
         <v>315.6291835365779</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="L33" t="n">
         <v>2.24</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>4.41</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>316</v>
+        <v>311.25</v>
       </c>
       <c r="I34" t="n">
         <v>312.3308845318511</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.57</v>
+        <v>-2.06</v>
       </c>
       <c r="L34" t="n">
-        <v>2.14</v>
+        <v>4.22</v>
       </c>
       <c r="M34" t="n">
         <v>0.64</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>4.16</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45383.38541666666</v>
+        <v>45383.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>303.65</v>
+        <v>306.1</v>
       </c>
       <c r="I35" t="n">
         <v>304.3605588900361</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>74</v>
+        <v>74.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>2.44</v>
+        <v>1.65</v>
       </c>
       <c r="L35" t="n">
         <v>3.94</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>4.77</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45442.38541666666</v>
+        <v>45442.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>678</v>
+        <v>665.5</v>
       </c>
       <c r="I36" t="n">
         <v>670.5097571973032</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>58.83333333333334</v>
+        <v>59</v>
       </c>
       <c r="K36" t="n">
-        <v>121.5</v>
+        <v>117.41</v>
       </c>
       <c r="L36" t="n">
         <v>0.83</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>14.2</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45477.55208333334</v>
+        <v>45478.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>686.7</v>
+        <v>694.5</v>
       </c>
       <c r="I37" t="n">
         <v>689.296742078032</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.19</v>
+        <v>-4.36</v>
       </c>
       <c r="L37" t="n">
         <v>11.19</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>7.25</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45491.38541666666</v>
+        <v>45491.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>652.75</v>
+        <v>647</v>
       </c>
       <c r="I38" t="n">
         <v>651.4081371534012</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.01</v>
+        <v>-6.84</v>
       </c>
       <c r="L38" t="n">
-        <v>6.41</v>
+        <v>6.98</v>
       </c>
       <c r="M38" t="n">
         <v>0.88</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.79</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45547.55208333334</v>
+        <v>45548.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>490</v>
+        <v>500.4</v>
       </c>
       <c r="I39" t="n">
         <v>500.0589678201964</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>56</v>
+        <v>56.83333333333334</v>
       </c>
       <c r="K39" t="n">
-        <v>24.27</v>
+        <v>22.66</v>
       </c>
       <c r="L39" t="n">
         <v>2.5</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.3</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>518.1</v>
+        <v>498.1</v>
       </c>
       <c r="I40" t="n">
         <v>501.6949184472688</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>3.54</v>
+        <v>-0.46</v>
       </c>
       <c r="L40" t="n">
         <v>4.37</v>
@@ -2721,7 +3200,7 @@
         <v>0.63</v>
       </c>
       <c r="N40" t="n">
-        <v>1.04</v>
+        <v>4.65</v>
       </c>
       <c r="O40" t="n">
         <v>1.43</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45588.55208333334</v>
+        <v>45589.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="I41" t="n">
         <v>528.6785687537157</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.2</v>
+        <v>-7.21</v>
       </c>
       <c r="L41" t="n">
-        <v>7.41</v>
+        <v>7.6</v>
       </c>
       <c r="M41" t="n">
         <v>3.87</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.27</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>559.75</v>
+        <v>516.15</v>
       </c>
       <c r="I42" t="n">
         <v>518.9212105644868</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>4.82</v>
+        <v>-3.34</v>
       </c>
       <c r="L42" t="n">
         <v>5.78</v>
       </c>
       <c r="M42" t="n">
-        <v>-0</v>
+        <v>7.1</v>
       </c>
       <c r="N42" t="n">
-        <v>4.51</v>
+        <v>8.02</v>
       </c>
       <c r="O42" t="n">
         <v>1.91</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>11.41</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>454</v>
+        <v>468.55</v>
       </c>
       <c r="I43" t="n">
         <v>459.1810065928636</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K43" t="n">
-        <v>12.04</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L43" t="n">
         <v>1.4</v>
@@ -2892,7 +3407,7 @@
         <v>1.57</v>
       </c>
       <c r="N43" t="n">
-        <v>2.25</v>
+        <v>3.38</v>
       </c>
       <c r="O43" t="n">
         <v>-8.02</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>7.29</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>449.25</v>
+        <v>437.1</v>
       </c>
       <c r="I44" t="n">
         <v>443.8172386472284</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.12</v>
+        <v>-6.71</v>
       </c>
       <c r="L44" t="n">
-        <v>5.02</v>
+        <v>7.72</v>
       </c>
       <c r="M44" t="n">
         <v>0.33</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>7.9</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>441.45</v>
+        <v>455.45</v>
       </c>
       <c r="I45" t="n">
         <v>450.2477985784403</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>-1</v>
+        <v>-4.2</v>
       </c>
       <c r="L45" t="n">
-        <v>3.67</v>
+        <v>5.22</v>
       </c>
       <c r="M45" t="n">
-        <v>0.38</v>
+        <v>1.71</v>
       </c>
       <c r="N45" t="n">
         <v>4.1</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>7.41</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45685.38541666666</v>
+        <v>45685.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>447</v>
+        <v>432.85</v>
       </c>
       <c r="I46" t="n">
         <v>446.1912278751761</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.86</v>
+        <v>-4.96</v>
       </c>
       <c r="L46" t="n">
-        <v>3.88</v>
+        <v>5.37</v>
       </c>
       <c r="M46" t="n">
         <v>1.2</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>12.09</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45692.55208333334</v>
+        <v>45693.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>437.9</v>
+        <v>465.5</v>
       </c>
       <c r="I47" t="n">
         <v>464.683716513154</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.17</v>
+        <v>-7.54</v>
       </c>
       <c r="L47" t="n">
-        <v>6.55</v>
+        <v>7.65</v>
       </c>
       <c r="M47" t="n">
         <v>1.65</v>
       </c>
       <c r="N47" t="n">
-        <v>1.54</v>
+        <v>6.07</v>
       </c>
       <c r="O47" t="n">
         <v>-3.98</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>10.76</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>435</v>
+        <v>414.15</v>
       </c>
       <c r="I48" t="n">
         <v>431.6528335957197</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.55</v>
+        <v>-11.03</v>
       </c>
       <c r="L48" t="n">
-        <v>6.98</v>
+        <v>11.06</v>
       </c>
       <c r="M48" t="n">
         <v>0.01</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>11.3</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>410.95</v>
+        <v>426.45</v>
       </c>
       <c r="I49" t="n">
         <v>415.1946262929984</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>0.77</v>
+        <v>-2.97</v>
       </c>
       <c r="L49" t="n">
         <v>5.87</v>
       </c>
       <c r="M49" t="n">
-        <v>0.54</v>
+        <v>1.72</v>
       </c>
       <c r="N49" t="n">
         <v>3.93</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>458.75</v>
+        <v>428.65</v>
       </c>
       <c r="I50" t="n">
         <v>431.1264685239431</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K50" t="n">
-        <v>7.57</v>
+        <v>0.52</v>
       </c>
       <c r="L50" t="n">
         <v>2.39</v>
@@ -3291,7 +3890,7 @@
         <v>1.17</v>
       </c>
       <c r="N50" t="n">
-        <v>2.38</v>
+        <v>7.03</v>
       </c>
       <c r="O50" t="n">
         <v>3.78</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.92</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>437.7</v>
+        <v>443</v>
       </c>
       <c r="I51" t="n">
         <v>438.2562371999532</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.11</v>
+        <v>-3.35</v>
       </c>
       <c r="L51" t="n">
         <v>6.79</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>9.09</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45782.55208333334</v>
+        <v>45783.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>428.6</v>
+        <v>416.65</v>
       </c>
       <c r="I52" t="n">
         <v>427.7739023600359</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.25</v>
+        <v>-5.95</v>
       </c>
       <c r="L52" t="n">
-        <v>3.72</v>
+        <v>6.07</v>
       </c>
       <c r="M52" t="n">
         <v>0.67</v>
       </c>
       <c r="N52" t="n">
-        <v>3.46</v>
+        <v>3.83</v>
       </c>
       <c r="O52" t="n">
         <v>0.64</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>8.57</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>409.3</v>
+        <v>433.3</v>
       </c>
       <c r="I53" t="n">
         <v>431.4052304670032</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
-        <v>1.76</v>
+        <v>-4</v>
       </c>
       <c r="L53" t="n">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>0.33</v>
+        <v>2.61</v>
       </c>
       <c r="N53" t="n">
-        <v>2.83</v>
+        <v>6.28</v>
       </c>
       <c r="O53" t="n">
         <v>-3.83</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.84</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45824.55208333334</v>
+        <v>45825.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>513.7</v>
+        <v>492.9</v>
       </c>
       <c r="I54" t="n">
         <v>498.2334872908741</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>18.56</v>
+        <v>13.75</v>
       </c>
       <c r="L54" t="n">
         <v>3.07</v>
@@ -3519,7 +4166,7 @@
         <v>2.17</v>
       </c>
       <c r="N54" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="O54" t="n">
         <v>6.28</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.08</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45856.55208333334</v>
+        <v>45859.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>435.4</v>
+        <v>446.2</v>
       </c>
       <c r="I55" t="n">
         <v>440.9904233556376</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K55" t="n">
-        <v>11.67</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="L55" t="n">
         <v>2.78</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>5.24</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45868.55208333334</v>
+        <v>45869.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>432.5</v>
+        <v>429</v>
       </c>
       <c r="I56" t="n">
         <v>431.2412715701726</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.07</v>
+        <v>-3.85</v>
       </c>
       <c r="L56" t="n">
-        <v>3.5</v>
+        <v>4.49</v>
       </c>
       <c r="M56" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="N56" t="n">
-        <v>1.56</v>
+        <v>2.43</v>
       </c>
       <c r="O56" t="n">
         <v>2.15</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>3.44</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45891.55208333334</v>
+        <v>45894.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>425.2</v>
+        <v>435.5</v>
       </c>
       <c r="I57" t="n">
         <v>433.9065586180226</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K57" t="n">
-        <v>0.89</v>
+        <v>-1.52</v>
       </c>
       <c r="L57" t="n">
-        <v>1.12</v>
+        <v>1.82</v>
       </c>
       <c r="M57" t="n">
         <v>1.84</v>
       </c>
       <c r="N57" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="O57" t="n">
         <v>-2.43</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.36</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45953.38541666666</v>
+        <v>45953.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>485.75</v>
+        <v>481.3</v>
       </c>
       <c r="I58" t="n">
         <v>481.7105493701315</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>59</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>11.54</v>
+        <v>10.52</v>
       </c>
       <c r="L58" t="n">
         <v>4.02</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.55</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45972.38541666666</v>
+        <v>45972.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>484.6</v>
+        <v>487.3</v>
       </c>
       <c r="I59" t="n">
         <v>486.6927326921694</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.25</v>
       </c>
       <c r="L59" t="n">
         <v>3.13</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>4.38</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45981.38541666666</v>
+        <v>45981.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>473.3</v>
+        <v>472</v>
       </c>
       <c r="I60" t="n">
         <v>473.2634180203956</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.87</v>
+        <v>-3.14</v>
       </c>
       <c r="L60" t="n">
         <v>3.92</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>4.31</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45987.55208333334</v>
+        <v>45988.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>470</v>
+        <v>474.6</v>
       </c>
       <c r="I61" t="n">
         <v>474.48340374655</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>0.42</v>
+        <v>-0.55</v>
       </c>
       <c r="L61" t="n">
-        <v>0.46</v>
+        <v>1.38</v>
       </c>
       <c r="M61" t="n">
-        <v>0.86</v>
+        <v>1.26</v>
       </c>
       <c r="N61" t="n">
         <v>1.96</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>3.87</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>628.65</v>
+        <v>595.7</v>
       </c>
       <c r="I62" t="n">
         <v>605.4215953808925</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K62" t="n">
-        <v>32.46</v>
+        <v>25.52</v>
       </c>
       <c r="L62" t="n">
         <v>0.41</v>
@@ -3975,7 +4718,7 @@
         <v>1.09</v>
       </c>
       <c r="N62" t="n">
-        <v>2.97</v>
+        <v>6.15</v>
       </c>
       <c r="O62" t="n">
         <v>0.96</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>9.27</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>631</v>
+        <v>658.5</v>
       </c>
       <c r="I63" t="n">
         <v>634.7439537705964</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.93</v>
+        <v>-10.54</v>
       </c>
       <c r="L63" t="n">
-        <v>6.9</v>
+        <v>12.63</v>
       </c>
       <c r="M63" t="n">
         <v>2.61</v>
       </c>
       <c r="N63" t="n">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="O63" t="n">
         <v>-6.15</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46051.55208333334</v>
+        <v>46052.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>715.9</v>
+        <v>644.15</v>
       </c>
       <c r="I64" t="n">
         <v>656.4624803993569</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K64" t="n">
-        <v>8.720000000000001</v>
+        <v>-2.18</v>
       </c>
       <c r="L64" t="n">
         <v>3.71</v>
       </c>
       <c r="M64" t="n">
-        <v>1.93</v>
+        <v>3.62</v>
       </c>
       <c r="N64" t="n">
-        <v>4.4</v>
+        <v>12.57</v>
       </c>
       <c r="O64" t="n">
         <v>3.8</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>16.15</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46118.55208333334</v>
+        <v>46119.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="I65" t="n">
         <v>530.6605669831481</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>67</v>
       </c>
       <c r="K65" t="n">
-        <v>18.5</v>
+        <v>17.57</v>
       </c>
       <c r="L65" t="n">
         <v>7.12</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.27</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46161.55208333334</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>632.4</v>
+        <v>628.7</v>
       </c>
       <c r="I66" t="n">
         <v>630.0826811524097</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K66" t="n">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="L66" t="n">
         <v>2.24</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.71</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46232.38541666666</v>
+        <v>46232.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>532.8</v>
+        <v>539.8</v>
       </c>
       <c r="I67" t="n">
         <v>539.6340851310442</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>70</v>
+        <v>70.16666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>15.25</v>
+        <v>14.14</v>
       </c>
       <c r="L67" t="n">
         <v>4.95</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>4.95</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46247.55208333334</v>
+        <v>46248.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>578</v>
+        <v>560.15</v>
       </c>
       <c r="I68" t="n">
         <v>572.7896704025669</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K68" t="n">
-        <v>7.08</v>
+        <v>3.77</v>
       </c>
       <c r="L68" t="n">
         <v>1.59</v>
       </c>
       <c r="M68" t="n">
-        <v>0.17</v>
+        <v>0.52</v>
       </c>
       <c r="N68" t="n">
-        <v>1.82</v>
+        <v>3.11</v>
       </c>
       <c r="O68" t="n">
         <v>2.27</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>7.68</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46254.55208333334</v>
+        <v>46255.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>573</v>
+        <v>594.3</v>
       </c>
       <c r="I69" t="n">
         <v>586.9619062001382</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.29</v>
+        <v>-6.1</v>
       </c>
       <c r="L69" t="n">
-        <v>2.83</v>
+        <v>6.29</v>
       </c>
       <c r="M69" t="n">
         <v>2.7</v>
       </c>
       <c r="N69" t="n">
-        <v>3.24</v>
+        <v>3.89</v>
       </c>
       <c r="O69" t="n">
         <v>-3.11</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.01</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46267.55208333334</v>
+        <v>46268.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>588</v>
+        <v>586.15</v>
       </c>
       <c r="I70" t="n">
         <v>586.5733417511225</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.06</v>
+        <v>-1.37</v>
       </c>
       <c r="L70" t="n">
         <v>2.47</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>72</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7462,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7472,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7482,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="11">
@@ -6683,7 +7542,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.97</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.12</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7562,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.76</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7572,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>121.5</v>
+        <v>117.41</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7582,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.1</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7592,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.65</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7602,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.41</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7612,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.19</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7622,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7632,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7642,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7652,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.93</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7662,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.08</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.88</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7682,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
